--- a/Result/profitability/1103.xlsx
+++ b/Result/profitability/1103.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.41</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2225</v>
+        <v>0.15375</v>
       </c>
       <c r="N2" t="n">
-        <v>17.34</v>
+        <v>17.82875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0.13375</v>
+        <v>0.195</v>
       </c>
       <c r="N3" t="n">
-        <v>17.40375</v>
+        <v>18.5825</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>0.18875</v>
+        <v>0.19625</v>
       </c>
       <c r="N4" t="n">
-        <v>17.8825</v>
+        <v>18.4175</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.16</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1525</v>
+        <v>0.23125</v>
       </c>
       <c r="N5" t="n">
-        <v>17.10625</v>
+        <v>17.55125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2</v>
+        <v>0.09375000000000003</v>
       </c>
       <c r="N6" t="n">
-        <v>15.8</v>
+        <v>16.395</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>0.12125</v>
+        <v>0.13</v>
       </c>
       <c r="N7" t="n">
-        <v>15.72625</v>
+        <v>16.23875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.37</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1525</v>
+        <v>0.16625</v>
       </c>
       <c r="N8" t="n">
-        <v>14.84625</v>
+        <v>14.74375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>-0.16</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.07000000000000002</v>
       </c>
       <c r="N10" t="n">
         <v>12.355</v>
@@ -1772,7 +1772,7 @@
         <v>-0.12</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05124999999999999</v>
+        <v>0.05125000000000003</v>
       </c>
       <c r="N11" t="n">
         <v>10.91875</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>667</v>
+      </c>
+      <c r="D75" t="n">
+        <v>532</v>
+      </c>
+      <c r="E75" t="n">
+        <v>136</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>135</v>
+      </c>
+      <c r="J75" t="n">
+        <v>137</v>
+      </c>
+      <c r="K75" t="n">
+        <v>126</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.6775</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.8200000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03877068557919627</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.431818181818182</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.559999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2122838401908169</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
